--- a/out/Attention-MambaAMT_repeat_3_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.066793665939915</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.066793665939915</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.3648012947504813</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.3648012947504813</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.734013026559911</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.666793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.666793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.3648012947504813</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.666793665939915</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.666793665939915</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.666793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.734013026559911</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.666793665939915</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002913298772085691</v>
+        <v>-0.0004039903106953716</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.374964035010552</v>
+        <v>0.5199669991956373</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7506381042279725</v>
+        <v>1.040918026072403</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0865947051257451</v>
+        <v>-0.1200817524375768</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.734013026559911</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2880780000075984</v>
+        <v>0.399481256447365</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.066793665939915</v>
+        <v>2.648249220197787</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2880780000075984</v>
+        <v>0.399481256447365</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.066793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2878333916456392</v>
+        <v>0.3989582150643412</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.751489789222873</v>
+        <v>1.606896084185417</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.666793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.79230936190588</v>
+        <v>3.615950414299784</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1437891036411327</v>
+        <v>0.3074614597603565</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.666793665939915</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.327301127687013</v>
+        <v>2.621632098629492</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2518600341746551</v>
+        <v>0.5385481233643566</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.734013026559911</v>
+        <v>3.248249220197787</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.687303012187501</v>
+        <v>3.391417476708383</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1379279583127036</v>
+        <v>0.2949283121793538</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.711081371058281</v>
+        <v>3.44226225872166</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.05696625546764007</v>
+        <v>0.1218096880558374</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.686941332185606</v>
+        <v>3.390644062821856</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07097457537792341</v>
+        <v>0.1517644183144333</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.771934770660984</v>
+        <v>3.572384244705274</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04273645292383951</v>
+        <v>0.09138237418680643</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.786383956336651</v>
+        <v>3.603280606049569</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03249029496996596</v>
+        <v>0.06947427252781777</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.808611629008205</v>
+        <v>3.650809525576605</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01437014673300932</v>
+        <v>0.03072865154027523</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.804833159388443</v>
+        <v>3.642731073546503</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01140296403134671</v>
+        <v>0.02438467710956912</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.81326321057781</v>
+        <v>3.660759120080173</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005650846875332712</v>
+        <v>0.0120896570730799</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.813157246991799</v>
+        <v>3.660538239712532</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003285306043307011</v>
+        <v>0.007029447402932231</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.814071522115813</v>
+        <v>3.662498586529389</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001638698421280691</v>
+        <v>0.003512223701466115</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.81406447560032</v>
+        <v>3.662489207348449</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008085254299540218</v>
+        <v>0.001731287490078548</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.814038882021225</v>
+        <v>3.662440220380595</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004656090416842858</v>
+        <v>0.001002971138926627</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.814164486448178</v>
+        <v>3.662714425370928</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001534698780920055</v>
+        <v>0.0003320274872097581</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.814002091471842</v>
+        <v>3.662373576931304</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.360269015448652e-05</v>
+        <v>0.0001656801271925993</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.813997975065556</v>
+        <v>3.662370465544498</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.903153034195311e-05</v>
+        <v>8.795545294412324e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.814000143127027</v>
+        <v>3.662380598118713</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>4.003342849230196e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.81399374642987</v>
+        <v>3.662372649535827</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>2.118280671066587e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.813993588952366</v>
+        <v>3.662377870626569</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>7.887479732251461e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.813986921988496</v>
+        <v>3.6623695334752</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.8139830599134</v>
+        <v>3.66236642878995</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.813978512601214</v>
+        <v>3.6623621097988</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.813978602545864</v>
+        <v>3.662357285625911</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.813977744612279</v>
+        <v>3.662356427692327</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.813977972933314</v>
+        <v>3.662356656013361</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.813977177269102</v>
+        <v>3.66235586034915</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.813977239538475</v>
+        <v>3.662355922618522</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.813977267213752</v>
+        <v>3.662355950293799</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.813977419427775</v>
+        <v>3.662356102507822</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.813977073486814</v>
+        <v>3.662355756566861</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.813977149593825</v>
+        <v>3.662355832673872</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.813977315645487</v>
+        <v>3.662355998725534</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.813977675424087</v>
+        <v>3.662356358504134</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.813977696180545</v>
+        <v>3.662356379260591</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.813977799962833</v>
+        <v>3.66235648304288</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.813978028283868</v>
+        <v>3.662356711363914</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.813977903745122</v>
+        <v>3.662356586825169</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.813977931420399</v>
+        <v>3.662356614500445</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.813977986770953</v>
+        <v>3.662356669851</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.813978249686083</v>
+        <v>3.66235693276613</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.813978166660253</v>
+        <v>3.662356849740299</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.813977959095675</v>
+        <v>3.662356642175723</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.813977972933314</v>
+        <v>3.662356656013361</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.813978111309699</v>
+        <v>3.662356794389745</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.81397782763811</v>
+        <v>3.662356510718157</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.813977654667629</v>
+        <v>3.662356337747676</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.813977550885341</v>
+        <v>3.662356233965387</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.813977696180545</v>
+        <v>3.662356379260591</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.813977938339218</v>
+        <v>3.662356621419265</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.813977765368737</v>
+        <v>3.662356448448784</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.81397746785951</v>
+        <v>3.662356150939557</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.813977454021872</v>
+        <v>3.662356137101919</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.813977087324452</v>
+        <v>3.662355770404499</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.813977087324452</v>
+        <v>3.662355770404499</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.813977025055079</v>
+        <v>3.662355708135126</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.813976921272791</v>
+        <v>3.662355604352837</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.81397674830231</v>
+        <v>3.662355431382357</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.813976796734044</v>
+        <v>3.662355479814092</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.813976436955445</v>
+        <v>3.662355120035491</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.813976395442529</v>
+        <v>3.662355078522576</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.813976450793083</v>
+        <v>3.66235513387313</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.813976506143637</v>
+        <v>3.662355189223684</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.813976547656552</v>
+        <v>3.662355230736599</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.813976277822602</v>
+        <v>3.662354960902649</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.813976333173156</v>
+        <v>3.662355016253203</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.81397647846836</v>
+        <v>3.662355161548407</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.813976443874264</v>
+        <v>3.66235512695431</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.813976430036625</v>
+        <v>3.662355113116672</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.813976519981275</v>
+        <v>3.662355203061322</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.81397683824696</v>
+        <v>3.662355521327007</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.81397665835766</v>
+        <v>3.662355341437707</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.813976699870575</v>
+        <v>3.662355382950623</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.813976513062456</v>
+        <v>3.662355196142503</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.813976582250648</v>
+        <v>3.662355265330695</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.813976381604891</v>
+        <v>3.662355064684938</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.813976423117806</v>
+        <v>3.662355106197853</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.813976450793083</v>
+        <v>3.66235513387313</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.734013026559911</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.666793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.066793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.734013026559911</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.666793665939915</v>
+        <v>0.2570455555016957</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002913298772085691</v>
+        <v>-0.0001295060358504998</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.374964035010552</v>
+        <v>0.1666843561743608</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554074</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7506381042279725</v>
+        <v>0.3336841593304349</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0865947051257451</v>
+        <v>-0.03849426910613526</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2880780000075984</v>
+        <v>0.1280605810323751</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2880780000075984</v>
+        <v>0.1280605810323751</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2878333916456392</v>
+        <v>0.1278624798402858</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.751489789222873</v>
+        <v>0.6086095430394801</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.79230936190588</v>
+        <v>1.34629377495299</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1437891036411327</v>
+        <v>0.1164506405558091</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.327301127687013</v>
+        <v>0.9696970414921497</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2518600341746551</v>
+        <v>0.2039741233531028</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.687303012187501</v>
+        <v>1.26125216633049</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1379279583127036</v>
+        <v>0.1117038909500014</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.711081371058281</v>
+        <v>1.280509576059195</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.05696625546764007</v>
+        <v>0.046135333738215</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.686941332185606</v>
+        <v>1.260959252087542</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07097457537792341</v>
+        <v>0.05748017635013952</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.771934770660984</v>
+        <v>1.329792996315059</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04273645292383951</v>
+        <v>0.03461108160565892</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.786383956336651</v>
+        <v>1.341494995670201</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03249029496996596</v>
+        <v>0.02631372645688067</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554074</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.808611629008205</v>
+        <v>1.359496577239726</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01437014673300932</v>
+        <v>0.01163656438024248</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.804833159388443</v>
+        <v>1.356435632300441</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01140296403134671</v>
+        <v>0.009233861871948489</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.81326321057781</v>
+        <v>1.363261848861717</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005650846875332712</v>
+        <v>0.004575210362111541</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.813157246991799</v>
+        <v>1.36317508271786</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003285306043307011</v>
+        <v>0.002659827882996659</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.814071522115813</v>
+        <v>1.363914606160473</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001638698421280691</v>
+        <v>0.00132741394149833</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.134013026559911</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.81406447560032</v>
+        <v>1.363907947215172</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008085254299540218</v>
+        <v>0.0006532944291854099</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.3831388313554074</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.814038882021225</v>
+        <v>1.363886283152935</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004656090416842858</v>
+        <v>0.000375492416680912</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554074</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.814164486448178</v>
+        <v>1.363986966988515</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001534698780920055</v>
+        <v>0.0001222222964963988</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.814002091471842</v>
+        <v>1.363854500630238</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.360269015448652e-05</v>
+        <v>6.012794327086025e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.813997975065556</v>
+        <v>1.363850221285272</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.903153034195311e-05</v>
+        <v>2.924674582151908e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.814000143127027</v>
+        <v>1.363850997089952</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.81399374642987</v>
+        <v>1.36384483466293</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.813993588952366</v>
+        <v>1.363844137517526</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.134013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.813986921988496</v>
+        <v>1.363837802656978</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.8139830599134</v>
+        <v>1.363833560046825</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.813978512601214</v>
+        <v>1.36383378836786</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.813978602545864</v>
+        <v>1.363833878312509</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.813977744612279</v>
+        <v>1.363833020378924</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.813977972933314</v>
+        <v>1.363833248699959</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.813977177269102</v>
+        <v>1.363832453035748</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.813977239538475</v>
+        <v>1.363832515305121</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.813977267213752</v>
+        <v>1.363832542980398</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.813977419427775</v>
+        <v>1.36383269519442</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.813977073486814</v>
+        <v>1.363832349253459</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.813977149593825</v>
+        <v>1.363832425360471</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.813977315645487</v>
+        <v>1.363832591412132</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.813977675424087</v>
+        <v>1.363832951190732</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.813977696180545</v>
+        <v>1.36383297194719</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554073</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.813977799962833</v>
+        <v>1.363833075729478</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.813978028283868</v>
+        <v>1.363833304050513</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.813977903745122</v>
+        <v>1.363833179511767</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.813977931420399</v>
+        <v>1.363833207187044</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.813977986770953</v>
+        <v>1.363833262537598</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.813978249686083</v>
+        <v>1.363833525452728</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.813978166660253</v>
+        <v>1.363833442426898</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.813977959095675</v>
+        <v>1.363833234862321</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.813977972933314</v>
+        <v>1.363833248699959</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.813978111309699</v>
+        <v>1.363833387076344</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.134013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.81397782763811</v>
+        <v>1.363833103404755</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.813977654667629</v>
+        <v>1.363832930434274</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.813977550885341</v>
+        <v>1.363832826651986</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.813977696180545</v>
+        <v>1.36383297194719</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.813977938339218</v>
+        <v>1.363833214105863</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.813977765368737</v>
+        <v>1.363833041135382</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.81397746785951</v>
+        <v>1.363832743626155</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.813977454021872</v>
+        <v>1.363832729788517</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.813977087324452</v>
+        <v>1.363832363091097</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.813977087324452</v>
+        <v>1.363832363091097</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.813977025055079</v>
+        <v>1.363832300821724</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.813976921272791</v>
+        <v>1.363832197039436</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.81397674830231</v>
+        <v>1.363832024068955</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.813976796734044</v>
+        <v>1.363832072500689</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.813976436955445</v>
+        <v>1.36383171272209</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.813976395442529</v>
+        <v>1.363831671209174</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.813976450793083</v>
+        <v>1.363831726559728</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.813976506143637</v>
+        <v>1.363831781910282</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.813976547656552</v>
+        <v>1.363831823423197</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.813976277822602</v>
+        <v>1.363831553589247</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.813976333173156</v>
+        <v>1.363831608939801</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.81397647846836</v>
+        <v>1.363831754235005</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.813976443874264</v>
+        <v>1.363831719640909</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.813976430036625</v>
+        <v>1.363831705803271</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.666793665939915</v>
+        <v>0.4570455555016958</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.813976519981275</v>
+        <v>1.36383179574792</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.81397683824696</v>
+        <v>1.363832114013605</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.81397665835766</v>
+        <v>1.363831934124305</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.813976699870575</v>
+        <v>1.36383197563722</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.813976513062456</v>
+        <v>1.363831788829101</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.813976582250648</v>
+        <v>1.363831858017293</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.813976381604891</v>
+        <v>1.363831657371536</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.813976423117806</v>
+        <v>1.363831698884451</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.813976450793083</v>
+        <v>1.363831726559728</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.0002651102840900421</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01307539641857147</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.04999999999999988</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.008384659886360168</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.097229942358799</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.005396138876676559</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.097229942358799</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.002407770603895187</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.097229942358799</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.006596703082323074</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.097229942358799</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0102701410651207</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.097229942358799</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00804588571190834</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.097229942358799</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.00187176838517189</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.097229942358799</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001620400696992874</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.16</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.009819377213716507</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.009169012308120728</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01207228004932404</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.008236192166805267</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.005985777825117111</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.007394097745418549</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0115521103143692</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01557058468461037</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.00679384171962738</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.00371352955698967</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.008070904761552811</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.00842583179473877</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01229478418827057</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.009871374815702438</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.008274480700492859</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.02261041104793549</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2570455555016958</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.005890924483537674</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.003459181636571884</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0006370358169078827</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.008899971842765808</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01344843581318855</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.097229942358799</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.009656455367803574</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.097229942358799</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.009966269135475159</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.097229942358799</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.007050730288028717</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.097229942358799</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.006157305091619492</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.097229942358799</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.005735460668802261</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.097229942358799</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.007301636040210724</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.097229942358799</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0007808580994606018</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0169818215072155</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.00246860459446907</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2570455555016958</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01535425707697868</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2570455555016958</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02424376457929611</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.004614591598510742</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2570455555016957</v>
+        <v>0.16</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001295060358504998</v>
+        <v>-0.000118366278514266</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1666843561743608</v>
+        <v>0.15234641027499</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.01498917490243912</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3831388313554074</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3336841593304349</v>
+        <v>0.3049815551255529</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.03849426910613526</v>
+        <v>-0.03518314527081071</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.02090620994567871</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3831388313554072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1280605810323751</v>
+        <v>0.1170448987256652</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.007785852998495102</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1280605810323751</v>
+        <v>0.1170448987256652</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.00629642978310585</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1278624798402858</v>
+        <v>0.1170009726260011</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6086095430394801</v>
+        <v>0.1349504780360494</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.004184409976005554</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.097229942358799</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.34629377495299</v>
+        <v>0.3871706466415653</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1164506405558091</v>
+        <v>0.02582119130021044</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.002177003771066666</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4570455555016958</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9696970414921497</v>
+        <v>0.303665741759626</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2039741233531028</v>
+        <v>0.04522848293143346</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.006142936646938324</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1831388313554072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.26125216633049</v>
+        <v>0.3683140495390836</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1117038909500014</v>
+        <v>0.02476876314468919</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.02055081725120544</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3831388313554072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.280509576059195</v>
+        <v>0.3725841086775253</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.046135333738215</v>
+        <v>0.01022875831532248</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.009648032486438751</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2570455555016958</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.260959252087542</v>
+        <v>0.3682479983568296</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05748017635013952</v>
+        <v>0.01274427880559965</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0008243843913078308</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.097229942358799</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.329792996315059</v>
+        <v>0.3835101531011164</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03461108160565892</v>
+        <v>0.007671670576294819</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.004588179290294647</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4570455555016958</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.341494995670201</v>
+        <v>0.3861024970765097</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02631372645688067</v>
+        <v>0.005832177978844669</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.007975473999977112</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3831388313554074</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.359496577239726</v>
+        <v>0.3900913770730312</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01163656438024248</v>
+        <v>0.002576010314472872</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01341130584478378</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3831388313554072</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.356435632300441</v>
+        <v>0.3894086927171196</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009233861871948489</v>
+        <v>0.002043035992362046</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01854654029011726</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2570455555016958</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.363261848861717</v>
+        <v>0.3909189450344716</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004575210362111541</v>
+        <v>0.001010600986901849</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01899826526641846</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.097229942358799</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.36317508271786</v>
+        <v>0.3908957983210045</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002659827882996659</v>
+        <v>0.0005855677513627969</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.003707721829414368</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.4570455555016958</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.363914606160473</v>
+        <v>0.3910562046305212</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00132741394149833</v>
+        <v>0.0002917384760542131</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.007690791040658951</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.4570455555016958</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.363907947215172</v>
+        <v>0.391050835171087</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006532944291854099</v>
+        <v>0.0001416070562814668</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.003255940973758698</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3831388313554074</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.363886283152935</v>
+        <v>0.3910421239607201</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000375492416680912</v>
+        <v>7.844131944756842e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.007592439651489258</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3831388313554074</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.363986966988515</v>
+        <v>0.3910606621432514</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001222222964963988</v>
+        <v>2.40156114816348e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01714295148849487</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.363854500630238</v>
+        <v>0.3910268433447673</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.012794327086025e-05</v>
+        <v>8.474746883626259e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.009725354611873627</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.363850221285272</v>
+        <v>0.3910220062834471</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>2.338588390325519e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.005050834268331528</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3831388313554072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.363850997089952</v>
+        <v>0.3910184016061165</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.005974844098091125</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3831388313554072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.36384483466293</v>
+        <v>0.3910130912289705</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002204820513725281</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3831388313554072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.363844137517526</v>
+        <v>0.3910091669426195</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0005341395735740662</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.363837802656978</v>
+        <v>0.3910088348392963</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0003096796572208405</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3831388313554072</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.363833560046825</v>
+        <v>0.391009215374354</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.0009926147758960724</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3831388313554072</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.36383378836786</v>
+        <v>0.3910094436953888</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.009463749825954437</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.363833878312509</v>
+        <v>0.3910095336400387</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002109941095113754</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8233232182125103</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.363833020378924</v>
+        <v>0.3910086757064539</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.008965127170085907</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.363833248699959</v>
+        <v>0.3910089040274886</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01290462911128998</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.363832453035748</v>
+        <v>0.3910081083632768</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.00795929878950119</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.363832515305121</v>
+        <v>0.3910081706326499</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.005942970514297485</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.363832542980398</v>
+        <v>0.3910081983079268</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01273491978645325</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.36383269519442</v>
+        <v>0.39100835052195</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01058551669120789</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.363832349253459</v>
+        <v>0.3910080045809883</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01126442849636078</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.16</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.363832425360471</v>
+        <v>0.391008080688</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.005637940019369125</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.4570455555016958</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.363832591412132</v>
+        <v>0.3910082467396616</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.005204152315855026</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.097229942358799</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.363832951190732</v>
+        <v>0.3910086065182616</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0009138211607933044</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4570455555016958</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.36383297194719</v>
+        <v>0.3910086272747193</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.009659521281719208</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1831388313554073</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.363833075729478</v>
+        <v>0.3910087310570078</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.008433036506175995</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8233232182125103</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.363833304050513</v>
+        <v>0.3910089593780425</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.008297212421894073</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3831388313554072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.363833179511767</v>
+        <v>0.3910088348392963</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.005200933665037155</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.363833207187044</v>
+        <v>0.3910088625145732</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0008175671100616455</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4570455555016958</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.363833262537598</v>
+        <v>0.3910089178651271</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001484006643295288</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.363833525452728</v>
+        <v>0.3910091807802578</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.004837166517972946</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.363833442426898</v>
+        <v>0.391009097754427</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.0004931949079036713</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3831388313554072</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.363833234862321</v>
+        <v>0.3910088901898502</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.001778066158294678</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3831388313554072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.363833248699959</v>
+        <v>0.3910089040274886</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003355402499437332</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.363833387076344</v>
+        <v>0.3910090424038733</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.002842482179403305</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.363833103404755</v>
+        <v>0.3910087587322846</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002242043614387512</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.363832930434274</v>
+        <v>0.3910085857618039</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003113958984613419</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.363832826651986</v>
+        <v>0.3910084819795154</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-5.608797073364258e-05</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.36383297194719</v>
+        <v>0.3910086272747193</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.0004764944314956665</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.363833214105863</v>
+        <v>0.3910088694333925</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005801111459732056</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.363833041135382</v>
+        <v>0.3910086964629115</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002330608665943146</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.363832743626155</v>
+        <v>0.3910083989536846</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005817398428916931</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.363832729788517</v>
+        <v>0.3910083851160461</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001182585954666138</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1831388313554072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.363832363091097</v>
+        <v>0.3910080184186269</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.001588404178619385</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1831388313554072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.363832363091097</v>
+        <v>0.3910080184186269</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01468922942876816</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1831388313554072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.363832300821724</v>
+        <v>0.3910079561492538</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01361890882253647</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8233232182125103</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.363832197039436</v>
+        <v>0.3910078523669653</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00891740620136261</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8233232182125103</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.363832024068955</v>
+        <v>0.3910076793964845</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01718273013830185</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.363832072500689</v>
+        <v>0.3910077278282191</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01132949441671371</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.36383171272209</v>
+        <v>0.391007368049619</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.0006658881902694702</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.363831671209174</v>
+        <v>0.3910073265367036</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.00780637189745903</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.363831726559728</v>
+        <v>0.3910073818872573</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.005182743072509766</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.363831781910282</v>
+        <v>0.3910074372378113</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01119983941316605</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.363831823423197</v>
+        <v>0.3910074787507267</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0001622810959815979</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.363831553589247</v>
+        <v>0.3910072089167766</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.000266198068857193</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.363831608939801</v>
+        <v>0.3910072642673305</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.006953172385692596</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8233232182125103</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.363831754235005</v>
+        <v>0.3910074095625344</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.006954073905944824</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.363831719640909</v>
+        <v>0.3910073749684382</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.004133157432079315</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4570455555016958</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.363831705803271</v>
+        <v>0.3910073611307996</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01803557947278023</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4570455555016958</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.36383179574792</v>
+        <v>0.3910074510754498</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01846607774496078</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1831388313554072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.363832114013605</v>
+        <v>0.3910077693411345</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0274294838309288</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8233232182125103</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.363831934124305</v>
+        <v>0.3910075894518343</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02030475437641144</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.36383197563722</v>
+        <v>0.3910076309647497</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.007267128676176071</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.363831788829101</v>
+        <v>0.3910074441566304</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01298264414072037</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.363831858017293</v>
+        <v>0.3910075133448229</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.0115436315536499</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.363831657371536</v>
+        <v>0.3910073126990651</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002187248319387436</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.5799999999999997</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.363831698884451</v>
+        <v>0.3910073542119805</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.017195925116539</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.1600000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.363831726559728</v>
+        <v>0.3910073818872573</v>
       </c>
     </row>
   </sheetData>
